--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6810.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6810.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -809,6 +814,21 @@
           <t>6810-12-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>6810-12-12-NWO-FG</t>
@@ -816,17 +836,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6810-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: M8@DRIVE, C4HEX@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6810-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6810-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6810-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6810-12-12-NWO-FG (PARTcommunity / CADENAS, M8@DRIVE=M8, C4HEX@HEX=C, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -837,6 +857,11 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>6810-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
